--- a/GameConfig/Datas/wave_spawn.xlsx
+++ b/GameConfig/Datas/wave_spawn.xlsx
@@ -369,7 +369,7 @@
         <x:v>2301</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>20,40</x:v>
+        <x:v>25,45</x:v>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>2001</x:v>
@@ -385,7 +385,7 @@
         <x:v>2302</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>40,60</x:v>
+        <x:v>50,70</x:v>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>2001</x:v>
@@ -401,7 +401,7 @@
         <x:v>2320</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>40,60</x:v>
+        <x:v>50,70</x:v>
       </x:c>
       <x:c r="D9" t="n">
         <x:v>2002</x:v>
@@ -417,7 +417,7 @@
         <x:v>2303</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>60,80</x:v>
+        <x:v>75,95</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>2001</x:v>
@@ -433,7 +433,7 @@
         <x:v>2304</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>80,100</x:v>
+        <x:v>100,120</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>2001</x:v>
@@ -449,7 +449,7 @@
         <x:v>2305</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>100,120</x:v>
+        <x:v>125,145</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>2001</x:v>
@@ -465,7 +465,7 @@
         <x:v>2321</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>100,120</x:v>
+        <x:v>125,145</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>2002</x:v>
@@ -481,7 +481,7 @@
         <x:v>2306</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>120,140</x:v>
+        <x:v>150,170</x:v>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>2001</x:v>
@@ -497,7 +497,7 @@
         <x:v>2307</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>140,160</x:v>
+        <x:v>175,195</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:v>2001</x:v>
@@ -513,7 +513,7 @@
         <x:v>2308</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>160,180</x:v>
+        <x:v>200,220</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>2001</x:v>
@@ -529,7 +529,7 @@
         <x:v>2309</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>180,200</x:v>
+        <x:v>225,245</x:v>
       </x:c>
       <x:c r="D17" t="n">
         <x:v>2003</x:v>
@@ -545,7 +545,7 @@
         <x:v>2310</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>200,220</x:v>
+        <x:v>250,270</x:v>
       </x:c>
       <x:c r="D18" t="n">
         <x:v>2001</x:v>
@@ -561,7 +561,7 @@
         <x:v>2311</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>220,240</x:v>
+        <x:v>275,295</x:v>
       </x:c>
       <x:c r="D19" t="n">
         <x:v>2001</x:v>
@@ -577,7 +577,7 @@
         <x:v>2312</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>240,260</x:v>
+        <x:v>300,320</x:v>
       </x:c>
       <x:c r="D20" t="n">
         <x:v>2001</x:v>
@@ -593,7 +593,7 @@
         <x:v>2322</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>240,260</x:v>
+        <x:v>300,320</x:v>
       </x:c>
       <x:c r="D21" t="n">
         <x:v>2002</x:v>
@@ -609,7 +609,7 @@
         <x:v>2313</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>260,280</x:v>
+        <x:v>325,345</x:v>
       </x:c>
       <x:c r="D22" t="n">
         <x:v>2001</x:v>
@@ -625,7 +625,7 @@
         <x:v>2314</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>280,300</x:v>
+        <x:v>350,370</x:v>
       </x:c>
       <x:c r="D23" t="n">
         <x:v>2001</x:v>
@@ -641,7 +641,7 @@
         <x:v>2315</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>300,320</x:v>
+        <x:v>375,395</x:v>
       </x:c>
       <x:c r="D24" t="n">
         <x:v>2001</x:v>
@@ -657,7 +657,7 @@
         <x:v>2323</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>300,320</x:v>
+        <x:v>375,395</x:v>
       </x:c>
       <x:c r="D25" t="n">
         <x:v>2002</x:v>
@@ -673,7 +673,7 @@
         <x:v>2316</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>320,340</x:v>
+        <x:v>400,420</x:v>
       </x:c>
       <x:c r="D26" t="n">
         <x:v>2001</x:v>
@@ -689,7 +689,7 @@
         <x:v>2317</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>340,360</x:v>
+        <x:v>425,445</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:v>2001</x:v>
@@ -705,7 +705,7 @@
         <x:v>2318</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>360,380</x:v>
+        <x:v>450,470</x:v>
       </x:c>
       <x:c r="D28" t="n">
         <x:v>2001</x:v>
@@ -721,7 +721,7 @@
         <x:v>2319</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>380,400</x:v>
+        <x:v>475,495</x:v>
       </x:c>
       <x:c r="D29" t="n">
         <x:v>2003</x:v>
